--- a/Treinamento/ReativacaoApolice.xlsx
+++ b/Treinamento/ReativacaoApolice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E829AE5-7164-46EE-9AEF-FEA486480140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69847F70-F44F-406E-9A58-2EB2D806C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Treinamento/ReativacaoApolice.xlsx
+++ b/Treinamento/ReativacaoApolice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB67CD4-694E-4550-A4B6-CEAF6C14760C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC53A337-E32E-48FE-A29C-448695B95565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
